--- a/01_DATA/RAW/RECEIPT.xlsx
+++ b/01_DATA/RAW/RECEIPT.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="167">
   <si>
     <t>DATE</t>
   </si>
@@ -160,7 +160,7 @@
     <t>RATNAMAN KUSHAL</t>
   </si>
   <si>
-    <t>2/29/2083</t>
+    <t>29/2/2083</t>
   </si>
   <si>
     <t>GYANI MAHARJAN</t>
@@ -181,9 +181,6 @@
     <t>NATUROPAATHY TREATMENT</t>
   </si>
   <si>
-    <t>2/30/2083</t>
-  </si>
-  <si>
     <t>PAHALMAN  GHARTI</t>
   </si>
   <si>
@@ -365,6 +362,156 @@
   </si>
   <si>
     <t>GAHAN RAYAMAJHI</t>
+  </si>
+  <si>
+    <t>TARA DEVI CHAULAGUIN</t>
+  </si>
+  <si>
+    <t>BASUNDHARA</t>
+  </si>
+  <si>
+    <t>DAY</t>
+  </si>
+  <si>
+    <t>KOMAL GURUNG</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>NATUROPATHY THERAPITIC TREATMENT  (ONLINE)</t>
+  </si>
+  <si>
+    <t>ONLINE 10 DAYS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATNA SHAHI </t>
+  </si>
+  <si>
+    <t>HEALING</t>
+  </si>
+  <si>
+    <t>10 DAY</t>
+  </si>
+  <si>
+    <t>AMAR MOKTAN</t>
+  </si>
+  <si>
+    <t>DOLAKHA</t>
+  </si>
+  <si>
+    <t>3 DAY</t>
+  </si>
+  <si>
+    <t>SHREYA SHERPA</t>
+  </si>
+  <si>
+    <t>NAYABASTI  BAUDHA</t>
+  </si>
+  <si>
+    <t>5 DAY</t>
+  </si>
+  <si>
+    <t>CHUDAMADI SHRESTHA</t>
+  </si>
+  <si>
+    <t>UDHAIPUR</t>
+  </si>
+  <si>
+    <t>1 HR</t>
+  </si>
+  <si>
+    <t>KUMAR PARIYAR</t>
+  </si>
+  <si>
+    <t>SHREYA SHESTHA</t>
+  </si>
+  <si>
+    <t>NAYABAZAR</t>
+  </si>
+  <si>
+    <t>4 DAY OF SHRIYA SHERPA</t>
+  </si>
+  <si>
+    <t>DANTA KUMARI GURUNG</t>
+  </si>
+  <si>
+    <t>LAMJUNG</t>
+  </si>
+  <si>
+    <t>KRISHNA BDR GURUNG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAKSHINKALI </t>
+  </si>
+  <si>
+    <t>10 DAYS</t>
+  </si>
+  <si>
+    <t>PHUNCHOK DOLMA</t>
+  </si>
+  <si>
+    <t>NUWAKOT</t>
+  </si>
+  <si>
+    <t>MUKUNDA PHUYAL</t>
+  </si>
+  <si>
+    <t>TARKESHWOR</t>
+  </si>
+  <si>
+    <t>SUDYA ARAYAL</t>
+  </si>
+  <si>
+    <t>BHANGAL</t>
+  </si>
+  <si>
+    <t>ADV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KALPANA DEVI   MALLA </t>
+  </si>
+  <si>
+    <t>KAPAN</t>
+  </si>
+  <si>
+    <t>VIDHHYA PUN</t>
+  </si>
+  <si>
+    <t>BAGLUN,HATTIGHOODA</t>
+  </si>
+  <si>
+    <t>MANJU  KHAKUREL</t>
+  </si>
+  <si>
+    <t>KABREPALANCHOWK</t>
+  </si>
+  <si>
+    <t>DIK PRASAD RAI</t>
+  </si>
+  <si>
+    <t>DHARAN,BIJAYAPUR</t>
+  </si>
+  <si>
+    <t>BHIM BAHADUR BISHOWKARMA</t>
+  </si>
+  <si>
+    <t>ITARI</t>
+  </si>
+  <si>
+    <t>GIRIBHAKTA RAI</t>
+  </si>
+  <si>
+    <t>TIKATHALI</t>
+  </si>
+  <si>
+    <t>RIMA SAPKOTA</t>
+  </si>
+  <si>
+    <t>RAMPYARI SAPKOTA</t>
+  </si>
+  <si>
+    <t>BIRGUNJ</t>
   </si>
 </sst>
 </file>
@@ -429,7 +576,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -439,6 +586,9 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -446,13 +596,25 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="165" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1458,7 +1620,7 @@
       <c r="A27" s="3">
         <v>135.0</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C27" s="3" t="s">
@@ -1482,7 +1644,7 @@
       <c r="A28" s="3">
         <v>136.0</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C28" s="3" t="s">
@@ -1506,7 +1668,7 @@
       <c r="A29" s="3">
         <v>137.0</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C29" s="3"/>
@@ -1520,8 +1682,8 @@
       <c r="A30" s="3">
         <v>138.0</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>56</v>
+      <c r="B30" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>50</v>
@@ -1544,14 +1706,14 @@
       <c r="A31" s="3">
         <v>139.0</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>19</v>
@@ -1572,10 +1734,10 @@
         <v>66903.0</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>19</v>
@@ -1596,10 +1758,10 @@
         <v>66908.0</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>19</v>
@@ -1620,10 +1782,10 @@
         <v>66908.0</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>19</v>
@@ -1644,10 +1806,10 @@
         <v>66909.0</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>19</v>
@@ -1668,10 +1830,10 @@
         <v>66909.0</v>
       </c>
       <c r="C36" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>19</v>
@@ -1716,10 +1878,10 @@
         <v>66911.0</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>19</v>
@@ -1729,7 +1891,7 @@
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
@@ -1740,10 +1902,10 @@
         <v>66911.0</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>19</v>
@@ -1764,7 +1926,7 @@
         <v>66912.0</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -1788,10 +1950,10 @@
         <v>66913.0</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>19</v>
@@ -1812,10 +1974,10 @@
         <v>66913.0</v>
       </c>
       <c r="C42" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>19</v>
@@ -1836,10 +1998,10 @@
         <v>66915.0</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>19</v>
@@ -1860,10 +2022,10 @@
         <v>66919.0</v>
       </c>
       <c r="C44" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>19</v>
@@ -1884,10 +2046,10 @@
         <v>66919.0</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>19</v>
@@ -1908,10 +2070,10 @@
         <v>66923.0</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>19</v>
@@ -1932,10 +2094,10 @@
         <v>66923.0</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>19</v>
@@ -1956,10 +2118,10 @@
         <v>66923.0</v>
       </c>
       <c r="C48" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>19</v>
@@ -2002,10 +2164,10 @@
         <v>66924.0</v>
       </c>
       <c r="C50" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>19</v>
@@ -2026,10 +2188,10 @@
         <v>66927.0</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>19</v>
@@ -2050,10 +2212,10 @@
         <v>66928.0</v>
       </c>
       <c r="C52" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>9</v>
@@ -2074,10 +2236,10 @@
         <v>66929.0</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>55</v>
@@ -2098,10 +2260,10 @@
         <v>66932.0</v>
       </c>
       <c r="C54" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>55</v>
@@ -2118,71 +2280,71 @@
       <c r="A55" s="3">
         <v>163.0</v>
       </c>
-      <c r="B55" s="5">
+      <c r="B55" s="6">
         <v>66937.0</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>62</v>
+      <c r="C55" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F55" s="6">
+      <c r="F55" s="7">
         <v>100000.0</v>
       </c>
       <c r="G55" s="3"/>
-      <c r="H55" s="6" t="s">
-        <v>91</v>
+      <c r="H55" s="7" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="3">
         <v>164.0</v>
       </c>
-      <c r="B56" s="5">
+      <c r="B56" s="6">
         <v>66937.0</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D56" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="E56" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E56" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F56" s="6">
+      <c r="F56" s="7">
         <v>20000.0</v>
       </c>
       <c r="G56" s="3"/>
-      <c r="H56" s="6" t="s">
-        <v>91</v>
+      <c r="H56" s="7" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="3">
         <v>165.0</v>
       </c>
-      <c r="B57" s="5">
+      <c r="B57" s="6">
         <v>66948.0</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D57" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D57" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F57" s="6">
+      <c r="E57" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F57" s="7">
         <v>10000.0</v>
       </c>
       <c r="G57" s="3"/>
-      <c r="H57" s="6" t="s">
+      <c r="H57" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2190,23 +2352,23 @@
       <c r="A58" s="3">
         <v>166.0</v>
       </c>
-      <c r="B58" s="5">
+      <c r="B58" s="6">
         <v>66946.0</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D58" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D58" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F58" s="6">
+      <c r="E58" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F58" s="7">
         <v>30000.0</v>
       </c>
       <c r="G58" s="3"/>
-      <c r="H58" s="6" t="s">
+      <c r="H58" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2214,23 +2376,23 @@
       <c r="A59" s="3">
         <v>167.0</v>
       </c>
-      <c r="B59" s="5">
+      <c r="B59" s="6">
         <v>66946.0</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D59" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F59" s="6">
+      <c r="E59" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F59" s="7">
         <v>50000.0</v>
       </c>
       <c r="G59" s="3"/>
-      <c r="H59" s="6" t="s">
+      <c r="H59" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2238,47 +2400,47 @@
       <c r="A60" s="3">
         <v>168.0</v>
       </c>
-      <c r="B60" s="5">
+      <c r="B60" s="6">
         <v>66951.0</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60" s="7">
+        <v>50000.0</v>
+      </c>
+      <c r="G60" s="3"/>
+      <c r="H60" s="7" t="s">
         <v>101</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F60" s="6">
-        <v>50000.0</v>
-      </c>
-      <c r="G60" s="3"/>
-      <c r="H60" s="6" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="3">
         <v>169.0</v>
       </c>
-      <c r="B61" s="5">
+      <c r="B61" s="6">
         <v>66952.0</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D61" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="E61" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E61" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="F61" s="6">
+      <c r="F61" s="7">
         <v>50400.0</v>
       </c>
       <c r="G61" s="3"/>
-      <c r="H61" s="6" t="s">
+      <c r="H61" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2286,23 +2448,23 @@
       <c r="A62" s="3">
         <v>170.0</v>
       </c>
-      <c r="B62" s="5">
+      <c r="B62" s="6">
         <v>66955.0</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C62" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D62" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D62" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="E62" s="6" t="s">
+      <c r="E62" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F62" s="6">
+      <c r="F62" s="7">
         <v>2000.0</v>
       </c>
       <c r="G62" s="3"/>
-      <c r="H62" s="6" t="s">
+      <c r="H62" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2310,23 +2472,23 @@
       <c r="A63" s="3">
         <v>171.0</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C63" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="D63" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E63" s="6" t="s">
+      <c r="E63" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F63" s="6">
+      <c r="F63" s="7">
         <v>2000.0</v>
       </c>
       <c r="G63" s="3"/>
-      <c r="H63" s="6" t="s">
+      <c r="H63" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2334,23 +2496,23 @@
       <c r="A64" s="3">
         <v>172.0</v>
       </c>
-      <c r="B64" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C64" s="6" t="s">
+      <c r="B64" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D64" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D64" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E64" s="6" t="s">
+      <c r="E64" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F64" s="6">
+      <c r="F64" s="7">
         <v>2000.0</v>
       </c>
       <c r="G64" s="3"/>
-      <c r="H64" s="6" t="s">
+      <c r="H64" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2358,23 +2520,23 @@
       <c r="A65" s="3">
         <v>173.0</v>
       </c>
-      <c r="B65" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C65" s="6" t="s">
+      <c r="B65" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D65" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D65" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E65" s="6" t="s">
+      <c r="E65" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F65" s="7">
         <v>2000.0</v>
       </c>
       <c r="G65" s="3"/>
-      <c r="H65" s="6" t="s">
+      <c r="H65" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2382,23 +2544,23 @@
       <c r="A66" s="3">
         <v>174.0</v>
       </c>
-      <c r="B66" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C66" s="6" t="s">
+      <c r="B66" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D66" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E66" s="6" t="s">
+      <c r="E66" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F66" s="6">
+      <c r="F66" s="7">
         <v>2000.0</v>
       </c>
       <c r="G66" s="3"/>
-      <c r="H66" s="6" t="s">
+      <c r="H66" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2406,1043 +2568,1353 @@
       <c r="A67" s="3">
         <v>175.0</v>
       </c>
-      <c r="B67" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>78</v>
+      <c r="B67" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="E67" s="3"/>
-      <c r="F67" s="6">
+      <c r="F67" s="7">
         <v>100000.0</v>
       </c>
       <c r="G67" s="3"/>
-      <c r="H67" s="6" t="s">
-        <v>91</v>
+      <c r="H67" s="7" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="3">
         <v>176.0</v>
       </c>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
+      <c r="B68" s="6">
+        <v>66965.0</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F68" s="7">
+        <v>3500.0</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="3">
         <v>177.0</v>
       </c>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
+      <c r="B69" s="6">
+        <v>66965.0</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F69" s="7">
+        <v>40000.0</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="3">
         <v>178.0</v>
       </c>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
+      <c r="B70" s="6">
+        <v>66966.0</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F70" s="7">
+        <v>40000.0</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H70" s="7" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="3">
         <v>179.0</v>
       </c>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
+      <c r="B71" s="6">
+        <v>66966.0</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71" s="7">
+        <v>10500.0</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="3">
         <v>180.0</v>
       </c>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
+      <c r="B72" s="6">
+        <v>66967.0</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F72" s="7">
+        <v>50000.0</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="3">
         <v>181.0</v>
       </c>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="7"/>
-      <c r="G73" s="7"/>
-      <c r="H73" s="7"/>
-      <c r="I73" s="8"/>
-      <c r="J73" s="8"/>
-      <c r="K73" s="8"/>
-      <c r="L73" s="8"/>
-      <c r="M73" s="8"/>
-      <c r="N73" s="8"/>
-      <c r="O73" s="8"/>
-      <c r="P73" s="8"/>
-      <c r="Q73" s="8"/>
-      <c r="R73" s="8"/>
-      <c r="S73" s="8"/>
-      <c r="T73" s="8"/>
-      <c r="U73" s="8"/>
-      <c r="V73" s="8"/>
-      <c r="W73" s="8"/>
-      <c r="X73" s="8"/>
-      <c r="Y73" s="8"/>
-      <c r="Z73" s="8"/>
+      <c r="B73" s="6">
+        <v>66968.0</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73" s="8">
+        <v>2000.0</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I73" s="9"/>
+      <c r="J73" s="9"/>
+      <c r="K73" s="9"/>
+      <c r="L73" s="9"/>
+      <c r="M73" s="9"/>
+      <c r="N73" s="9"/>
+      <c r="O73" s="9"/>
+      <c r="P73" s="9"/>
+      <c r="Q73" s="9"/>
+      <c r="R73" s="9"/>
+      <c r="S73" s="9"/>
+      <c r="T73" s="9"/>
+      <c r="U73" s="9"/>
+      <c r="V73" s="9"/>
+      <c r="W73" s="9"/>
+      <c r="X73" s="9"/>
+      <c r="Y73" s="9"/>
+      <c r="Z73" s="9"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="3">
         <v>182.0</v>
       </c>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="8"/>
-      <c r="M74" s="8"/>
-      <c r="N74" s="8"/>
-      <c r="O74" s="8"/>
-      <c r="P74" s="8"/>
-      <c r="Q74" s="8"/>
-      <c r="R74" s="8"/>
-      <c r="S74" s="8"/>
-      <c r="T74" s="8"/>
-      <c r="U74" s="8"/>
-      <c r="V74" s="8"/>
-      <c r="W74" s="8"/>
-      <c r="X74" s="8"/>
-      <c r="Y74" s="8"/>
-      <c r="Z74" s="8"/>
+      <c r="B74" s="6">
+        <v>66970.0</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F74" s="11">
+        <v>3500.0</v>
+      </c>
+      <c r="G74" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="H74" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="I74" s="9"/>
+      <c r="J74" s="9"/>
+      <c r="K74" s="9"/>
+      <c r="L74" s="9"/>
+      <c r="M74" s="9"/>
+      <c r="N74" s="9"/>
+      <c r="O74" s="9"/>
+      <c r="P74" s="9"/>
+      <c r="Q74" s="9"/>
+      <c r="R74" s="9"/>
+      <c r="S74" s="9"/>
+      <c r="T74" s="9"/>
+      <c r="U74" s="9"/>
+      <c r="V74" s="9"/>
+      <c r="W74" s="9"/>
+      <c r="X74" s="9"/>
+      <c r="Y74" s="9"/>
+      <c r="Z74" s="9"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="3">
         <v>183.0</v>
       </c>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7"/>
-      <c r="G75" s="7"/>
-      <c r="H75" s="7"/>
-      <c r="I75" s="8"/>
-      <c r="J75" s="8"/>
-      <c r="K75" s="8"/>
-      <c r="L75" s="8"/>
-      <c r="M75" s="8"/>
-      <c r="N75" s="8"/>
-      <c r="O75" s="8"/>
-      <c r="P75" s="8"/>
-      <c r="Q75" s="8"/>
-      <c r="R75" s="8"/>
-      <c r="S75" s="8"/>
-      <c r="T75" s="8"/>
-      <c r="U75" s="8"/>
-      <c r="V75" s="8"/>
-      <c r="W75" s="8"/>
-      <c r="X75" s="8"/>
-      <c r="Y75" s="8"/>
-      <c r="Z75" s="8"/>
+      <c r="B75" s="6">
+        <v>66975.0</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F75" s="8">
+        <v>4000.0</v>
+      </c>
+      <c r="G75" s="13"/>
+      <c r="H75" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I75" s="9"/>
+      <c r="J75" s="9"/>
+      <c r="K75" s="9"/>
+      <c r="L75" s="9"/>
+      <c r="M75" s="9"/>
+      <c r="N75" s="9"/>
+      <c r="O75" s="9"/>
+      <c r="P75" s="9"/>
+      <c r="Q75" s="9"/>
+      <c r="R75" s="9"/>
+      <c r="S75" s="9"/>
+      <c r="T75" s="9"/>
+      <c r="U75" s="9"/>
+      <c r="V75" s="9"/>
+      <c r="W75" s="9"/>
+      <c r="X75" s="9"/>
+      <c r="Y75" s="9"/>
+      <c r="Z75" s="9"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="3">
         <v>184.0</v>
       </c>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
-      <c r="I76" s="8"/>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="8"/>
-      <c r="M76" s="8"/>
-      <c r="N76" s="8"/>
-      <c r="O76" s="8"/>
-      <c r="P76" s="8"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="8"/>
-      <c r="U76" s="8"/>
-      <c r="V76" s="8"/>
-      <c r="W76" s="8"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="8"/>
-      <c r="Z76" s="8"/>
+      <c r="B76" s="6">
+        <v>66975.0</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F76" s="12">
+        <v>40000.0</v>
+      </c>
+      <c r="G76" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="H76" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="I76" s="9"/>
+      <c r="J76" s="9"/>
+      <c r="K76" s="9"/>
+      <c r="L76" s="9"/>
+      <c r="M76" s="9"/>
+      <c r="N76" s="9"/>
+      <c r="O76" s="9"/>
+      <c r="P76" s="9"/>
+      <c r="Q76" s="9"/>
+      <c r="R76" s="9"/>
+      <c r="S76" s="9"/>
+      <c r="T76" s="9"/>
+      <c r="U76" s="9"/>
+      <c r="V76" s="9"/>
+      <c r="W76" s="9"/>
+      <c r="X76" s="9"/>
+      <c r="Y76" s="9"/>
+      <c r="Z76" s="9"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="3">
         <v>185.0</v>
       </c>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="7"/>
-      <c r="G77" s="7"/>
-      <c r="H77" s="7"/>
-      <c r="I77" s="8"/>
-      <c r="J77" s="8"/>
-      <c r="K77" s="8"/>
-      <c r="L77" s="8"/>
-      <c r="M77" s="8"/>
-      <c r="N77" s="8"/>
-      <c r="O77" s="8"/>
-      <c r="P77" s="8"/>
-      <c r="Q77" s="8"/>
-      <c r="R77" s="8"/>
-      <c r="S77" s="8"/>
-      <c r="T77" s="8"/>
-      <c r="U77" s="8"/>
-      <c r="V77" s="8"/>
-      <c r="W77" s="8"/>
-      <c r="X77" s="8"/>
-      <c r="Y77" s="8"/>
-      <c r="Z77" s="8"/>
+      <c r="B77" s="6">
+        <v>66982.0</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F77" s="8">
+        <v>4000.0</v>
+      </c>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="9"/>
+      <c r="K77" s="9"/>
+      <c r="L77" s="9"/>
+      <c r="M77" s="9"/>
+      <c r="N77" s="9"/>
+      <c r="O77" s="9"/>
+      <c r="P77" s="9"/>
+      <c r="Q77" s="9"/>
+      <c r="R77" s="9"/>
+      <c r="S77" s="9"/>
+      <c r="T77" s="9"/>
+      <c r="U77" s="9"/>
+      <c r="V77" s="9"/>
+      <c r="W77" s="9"/>
+      <c r="X77" s="9"/>
+      <c r="Y77" s="9"/>
+      <c r="Z77" s="9"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="3">
         <v>186.0</v>
       </c>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
-      <c r="I78" s="8"/>
-      <c r="J78" s="8"/>
-      <c r="K78" s="8"/>
-      <c r="L78" s="8"/>
-      <c r="M78" s="8"/>
-      <c r="N78" s="8"/>
-      <c r="O78" s="8"/>
-      <c r="P78" s="8"/>
-      <c r="Q78" s="8"/>
-      <c r="R78" s="8"/>
-      <c r="S78" s="8"/>
-      <c r="T78" s="8"/>
-      <c r="U78" s="8"/>
-      <c r="V78" s="8"/>
-      <c r="W78" s="8"/>
-      <c r="X78" s="8"/>
-      <c r="Y78" s="8"/>
-      <c r="Z78" s="8"/>
+      <c r="B78" s="14">
+        <v>66978.0</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F78" s="12">
+        <v>35000.0</v>
+      </c>
+      <c r="G78" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="H78" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I78" s="9"/>
+      <c r="J78" s="9"/>
+      <c r="K78" s="9"/>
+      <c r="L78" s="9"/>
+      <c r="M78" s="9"/>
+      <c r="N78" s="9"/>
+      <c r="O78" s="9"/>
+      <c r="P78" s="9"/>
+      <c r="Q78" s="9"/>
+      <c r="R78" s="9"/>
+      <c r="S78" s="9"/>
+      <c r="T78" s="9"/>
+      <c r="U78" s="9"/>
+      <c r="V78" s="9"/>
+      <c r="W78" s="9"/>
+      <c r="X78" s="9"/>
+      <c r="Y78" s="9"/>
+      <c r="Z78" s="9"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="3">
         <v>187.0</v>
       </c>
-      <c r="B79" s="7"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="7"/>
-      <c r="G79" s="7"/>
-      <c r="H79" s="7"/>
-      <c r="I79" s="8"/>
-      <c r="J79" s="8"/>
-      <c r="K79" s="8"/>
-      <c r="L79" s="8"/>
-      <c r="M79" s="8"/>
-      <c r="N79" s="8"/>
-      <c r="O79" s="8"/>
-      <c r="P79" s="8"/>
-      <c r="Q79" s="8"/>
-      <c r="R79" s="8"/>
-      <c r="S79" s="8"/>
-      <c r="T79" s="8"/>
-      <c r="U79" s="8"/>
-      <c r="V79" s="8"/>
-      <c r="W79" s="8"/>
-      <c r="X79" s="8"/>
-      <c r="Y79" s="8"/>
-      <c r="Z79" s="8"/>
+      <c r="B79" s="14">
+        <v>66978.0</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F79" s="8">
+        <v>10000.0</v>
+      </c>
+      <c r="G79" s="13"/>
+      <c r="H79" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I79" s="9"/>
+      <c r="J79" s="9"/>
+      <c r="K79" s="9"/>
+      <c r="L79" s="9"/>
+      <c r="M79" s="9"/>
+      <c r="N79" s="9"/>
+      <c r="O79" s="9"/>
+      <c r="P79" s="9"/>
+      <c r="Q79" s="9"/>
+      <c r="R79" s="9"/>
+      <c r="S79" s="9"/>
+      <c r="T79" s="9"/>
+      <c r="U79" s="9"/>
+      <c r="V79" s="9"/>
+      <c r="W79" s="9"/>
+      <c r="X79" s="9"/>
+      <c r="Y79" s="9"/>
+      <c r="Z79" s="9"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="3">
         <v>188.0</v>
       </c>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
-      <c r="I80" s="8"/>
-      <c r="J80" s="8"/>
-      <c r="K80" s="8"/>
-      <c r="L80" s="8"/>
-      <c r="M80" s="8"/>
-      <c r="N80" s="8"/>
-      <c r="O80" s="8"/>
-      <c r="P80" s="8"/>
-      <c r="Q80" s="8"/>
-      <c r="R80" s="8"/>
-      <c r="S80" s="8"/>
-      <c r="T80" s="8"/>
-      <c r="U80" s="8"/>
-      <c r="V80" s="8"/>
-      <c r="W80" s="8"/>
-      <c r="X80" s="8"/>
-      <c r="Y80" s="8"/>
-      <c r="Z80" s="8"/>
+      <c r="B80" s="14">
+        <v>66983.0</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F80" s="12">
+        <v>5000.0</v>
+      </c>
+      <c r="G80" s="13"/>
+      <c r="H80" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I80" s="9"/>
+      <c r="J80" s="9"/>
+      <c r="K80" s="9"/>
+      <c r="L80" s="9"/>
+      <c r="M80" s="9"/>
+      <c r="N80" s="9"/>
+      <c r="O80" s="9"/>
+      <c r="P80" s="9"/>
+      <c r="Q80" s="9"/>
+      <c r="R80" s="9"/>
+      <c r="S80" s="9"/>
+      <c r="T80" s="9"/>
+      <c r="U80" s="9"/>
+      <c r="V80" s="9"/>
+      <c r="W80" s="9"/>
+      <c r="X80" s="9"/>
+      <c r="Y80" s="9"/>
+      <c r="Z80" s="9"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="3">
         <v>189.0</v>
       </c>
-      <c r="B81" s="7"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7"/>
-      <c r="G81" s="7"/>
-      <c r="H81" s="7"/>
-      <c r="I81" s="8"/>
-      <c r="J81" s="8"/>
-      <c r="K81" s="8"/>
-      <c r="L81" s="8"/>
-      <c r="M81" s="8"/>
-      <c r="N81" s="8"/>
-      <c r="O81" s="8"/>
-      <c r="P81" s="8"/>
-      <c r="Q81" s="8"/>
-      <c r="R81" s="8"/>
-      <c r="S81" s="8"/>
-      <c r="T81" s="8"/>
-      <c r="U81" s="8"/>
-      <c r="V81" s="8"/>
-      <c r="W81" s="8"/>
-      <c r="X81" s="8"/>
-      <c r="Y81" s="8"/>
-      <c r="Z81" s="8"/>
+      <c r="B81" s="14">
+        <v>66983.0</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F81" s="8">
+        <v>20000.0</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="H81" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="I81" s="9"/>
+      <c r="J81" s="9"/>
+      <c r="K81" s="9"/>
+      <c r="L81" s="9"/>
+      <c r="M81" s="9"/>
+      <c r="N81" s="9"/>
+      <c r="O81" s="9"/>
+      <c r="P81" s="9"/>
+      <c r="Q81" s="9"/>
+      <c r="R81" s="9"/>
+      <c r="S81" s="9"/>
+      <c r="T81" s="9"/>
+      <c r="U81" s="9"/>
+      <c r="V81" s="9"/>
+      <c r="W81" s="9"/>
+      <c r="X81" s="9"/>
+      <c r="Y81" s="9"/>
+      <c r="Z81" s="9"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="3">
         <v>190.0</v>
       </c>
-      <c r="B82" s="9"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
-      <c r="F82" s="9"/>
-      <c r="G82" s="9"/>
-      <c r="H82" s="9"/>
-      <c r="I82" s="8"/>
-      <c r="J82" s="8"/>
-      <c r="K82" s="8"/>
-      <c r="L82" s="8"/>
-      <c r="M82" s="8"/>
-      <c r="N82" s="8"/>
-      <c r="O82" s="8"/>
-      <c r="P82" s="8"/>
-      <c r="Q82" s="8"/>
-      <c r="R82" s="8"/>
-      <c r="S82" s="8"/>
-      <c r="T82" s="8"/>
-      <c r="U82" s="8"/>
-      <c r="V82" s="8"/>
-      <c r="W82" s="8"/>
-      <c r="X82" s="8"/>
-      <c r="Y82" s="8"/>
-      <c r="Z82" s="8"/>
+      <c r="B82" s="14">
+        <v>66992.0</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E82" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F82" s="12">
+        <v>2000.0</v>
+      </c>
+      <c r="G82" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="H82" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I82" s="9"/>
+      <c r="J82" s="9"/>
+      <c r="K82" s="9"/>
+      <c r="L82" s="9"/>
+      <c r="M82" s="9"/>
+      <c r="N82" s="9"/>
+      <c r="O82" s="9"/>
+      <c r="P82" s="9"/>
+      <c r="Q82" s="9"/>
+      <c r="R82" s="9"/>
+      <c r="S82" s="9"/>
+      <c r="T82" s="9"/>
+      <c r="U82" s="9"/>
+      <c r="V82" s="9"/>
+      <c r="W82" s="9"/>
+      <c r="X82" s="9"/>
+      <c r="Y82" s="9"/>
+      <c r="Z82" s="9"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="3">
         <v>191.0</v>
       </c>
-      <c r="B83" s="7"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="7"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="7"/>
-      <c r="G83" s="7"/>
-      <c r="H83" s="7"/>
-      <c r="I83" s="8"/>
-      <c r="J83" s="8"/>
-      <c r="K83" s="8"/>
-      <c r="L83" s="8"/>
-      <c r="M83" s="8"/>
-      <c r="N83" s="8"/>
-      <c r="O83" s="8"/>
-      <c r="P83" s="8"/>
-      <c r="Q83" s="8"/>
-      <c r="R83" s="8"/>
-      <c r="S83" s="8"/>
-      <c r="T83" s="8"/>
-      <c r="U83" s="8"/>
-      <c r="V83" s="8"/>
-      <c r="W83" s="8"/>
-      <c r="X83" s="8"/>
-      <c r="Y83" s="8"/>
-      <c r="Z83" s="8"/>
+      <c r="B83" s="14">
+        <v>66992.0</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="D83" s="13"/>
+      <c r="E83" s="13"/>
+      <c r="F83" s="13"/>
+      <c r="G83" s="13"/>
+      <c r="H83" s="13"/>
+      <c r="I83" s="9"/>
+      <c r="J83" s="9"/>
+      <c r="K83" s="9"/>
+      <c r="L83" s="9"/>
+      <c r="M83" s="9"/>
+      <c r="N83" s="9"/>
+      <c r="O83" s="9"/>
+      <c r="P83" s="9"/>
+      <c r="Q83" s="9"/>
+      <c r="R83" s="9"/>
+      <c r="S83" s="9"/>
+      <c r="T83" s="9"/>
+      <c r="U83" s="9"/>
+      <c r="V83" s="9"/>
+      <c r="W83" s="9"/>
+      <c r="X83" s="9"/>
+      <c r="Y83" s="9"/>
+      <c r="Z83" s="9"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="3">
         <v>192.0</v>
       </c>
-      <c r="B84" s="9"/>
-      <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="9"/>
-      <c r="F84" s="9"/>
-      <c r="G84" s="9"/>
-      <c r="H84" s="9"/>
-      <c r="I84" s="8"/>
-      <c r="J84" s="8"/>
-      <c r="K84" s="8"/>
-      <c r="L84" s="8"/>
-      <c r="M84" s="8"/>
-      <c r="N84" s="8"/>
-      <c r="O84" s="8"/>
-      <c r="P84" s="8"/>
-      <c r="Q84" s="8"/>
-      <c r="R84" s="8"/>
-      <c r="S84" s="8"/>
-      <c r="T84" s="8"/>
-      <c r="U84" s="8"/>
-      <c r="V84" s="8"/>
-      <c r="W84" s="8"/>
-      <c r="X84" s="8"/>
-      <c r="Y84" s="8"/>
-      <c r="Z84" s="8"/>
+      <c r="B84" s="14">
+        <v>66993.0</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F84" s="12">
+        <v>48000.0</v>
+      </c>
+      <c r="G84" s="10"/>
+      <c r="H84" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I84" s="9"/>
+      <c r="J84" s="9"/>
+      <c r="K84" s="9"/>
+      <c r="L84" s="9"/>
+      <c r="M84" s="9"/>
+      <c r="N84" s="9"/>
+      <c r="O84" s="9"/>
+      <c r="P84" s="9"/>
+      <c r="Q84" s="9"/>
+      <c r="R84" s="9"/>
+      <c r="S84" s="9"/>
+      <c r="T84" s="9"/>
+      <c r="U84" s="9"/>
+      <c r="V84" s="9"/>
+      <c r="W84" s="9"/>
+      <c r="X84" s="9"/>
+      <c r="Y84" s="9"/>
+      <c r="Z84" s="9"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="3">
         <v>193.0</v>
       </c>
-      <c r="B85" s="7"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="7"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="7"/>
-      <c r="G85" s="7"/>
-      <c r="H85" s="7"/>
-      <c r="I85" s="8"/>
-      <c r="J85" s="8"/>
-      <c r="K85" s="8"/>
-      <c r="L85" s="8"/>
-      <c r="M85" s="8"/>
-      <c r="N85" s="8"/>
-      <c r="O85" s="8"/>
-      <c r="P85" s="8"/>
-      <c r="Q85" s="8"/>
-      <c r="R85" s="8"/>
-      <c r="S85" s="8"/>
-      <c r="T85" s="8"/>
-      <c r="U85" s="8"/>
-      <c r="V85" s="8"/>
-      <c r="W85" s="8"/>
-      <c r="X85" s="8"/>
-      <c r="Y85" s="8"/>
-      <c r="Z85" s="8"/>
+      <c r="B85" s="14">
+        <v>66997.0</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F85" s="8">
+        <v>5000.0</v>
+      </c>
+      <c r="G85" s="13"/>
+      <c r="H85" s="13"/>
+      <c r="I85" s="9"/>
+      <c r="J85" s="9"/>
+      <c r="K85" s="9"/>
+      <c r="L85" s="9"/>
+      <c r="M85" s="9"/>
+      <c r="N85" s="9"/>
+      <c r="O85" s="9"/>
+      <c r="P85" s="9"/>
+      <c r="Q85" s="9"/>
+      <c r="R85" s="9"/>
+      <c r="S85" s="9"/>
+      <c r="T85" s="9"/>
+      <c r="U85" s="9"/>
+      <c r="V85" s="9"/>
+      <c r="W85" s="9"/>
+      <c r="X85" s="9"/>
+      <c r="Y85" s="9"/>
+      <c r="Z85" s="9"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="3">
         <v>194.0</v>
       </c>
-      <c r="B86" s="9"/>
-      <c r="C86" s="9"/>
-      <c r="D86" s="9"/>
-      <c r="E86" s="9"/>
-      <c r="F86" s="9"/>
-      <c r="G86" s="9"/>
-      <c r="H86" s="9"/>
-      <c r="I86" s="8"/>
-      <c r="J86" s="8"/>
-      <c r="K86" s="8"/>
-      <c r="L86" s="8"/>
-      <c r="M86" s="8"/>
-      <c r="N86" s="8"/>
-      <c r="O86" s="8"/>
-      <c r="P86" s="8"/>
-      <c r="Q86" s="8"/>
-      <c r="R86" s="8"/>
-      <c r="S86" s="8"/>
-      <c r="T86" s="8"/>
-      <c r="U86" s="8"/>
-      <c r="V86" s="8"/>
-      <c r="W86" s="8"/>
-      <c r="X86" s="8"/>
-      <c r="Y86" s="8"/>
-      <c r="Z86" s="8"/>
+      <c r="B86" s="14">
+        <v>66997.0</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F86" s="12">
+        <v>50000.0</v>
+      </c>
+      <c r="G86" s="10"/>
+      <c r="H86" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I86" s="9"/>
+      <c r="J86" s="9"/>
+      <c r="K86" s="9"/>
+      <c r="L86" s="9"/>
+      <c r="M86" s="9"/>
+      <c r="N86" s="9"/>
+      <c r="O86" s="9"/>
+      <c r="P86" s="9"/>
+      <c r="Q86" s="9"/>
+      <c r="R86" s="9"/>
+      <c r="S86" s="9"/>
+      <c r="T86" s="9"/>
+      <c r="U86" s="9"/>
+      <c r="V86" s="9"/>
+      <c r="W86" s="9"/>
+      <c r="X86" s="9"/>
+      <c r="Y86" s="9"/>
+      <c r="Z86" s="9"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="3">
         <v>195.0</v>
       </c>
-      <c r="B87" s="7"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="7"/>
-      <c r="G87" s="7"/>
-      <c r="H87" s="7"/>
-      <c r="I87" s="8"/>
-      <c r="J87" s="8"/>
-      <c r="K87" s="8"/>
-      <c r="L87" s="8"/>
-      <c r="M87" s="8"/>
-      <c r="N87" s="8"/>
-      <c r="O87" s="8"/>
-      <c r="P87" s="8"/>
-      <c r="Q87" s="8"/>
-      <c r="R87" s="8"/>
-      <c r="S87" s="8"/>
-      <c r="T87" s="8"/>
-      <c r="U87" s="8"/>
-      <c r="V87" s="8"/>
-      <c r="W87" s="8"/>
-      <c r="X87" s="8"/>
-      <c r="Y87" s="8"/>
-      <c r="Z87" s="8"/>
+      <c r="B87" s="14">
+        <v>66997.0</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F87" s="8">
+        <v>21000.0</v>
+      </c>
+      <c r="G87" s="13"/>
+      <c r="H87" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I87" s="9"/>
+      <c r="J87" s="9"/>
+      <c r="K87" s="9"/>
+      <c r="L87" s="9"/>
+      <c r="M87" s="9"/>
+      <c r="N87" s="9"/>
+      <c r="O87" s="9"/>
+      <c r="P87" s="9"/>
+      <c r="Q87" s="9"/>
+      <c r="R87" s="9"/>
+      <c r="S87" s="9"/>
+      <c r="T87" s="9"/>
+      <c r="U87" s="9"/>
+      <c r="V87" s="9"/>
+      <c r="W87" s="9"/>
+      <c r="X87" s="9"/>
+      <c r="Y87" s="9"/>
+      <c r="Z87" s="9"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="3">
         <v>196.0</v>
       </c>
-      <c r="B88" s="9"/>
-      <c r="C88" s="9"/>
-      <c r="D88" s="9"/>
-      <c r="E88" s="9"/>
-      <c r="F88" s="9"/>
-      <c r="G88" s="9"/>
-      <c r="H88" s="9"/>
-      <c r="I88" s="8"/>
-      <c r="J88" s="8"/>
-      <c r="K88" s="8"/>
-      <c r="L88" s="8"/>
-      <c r="M88" s="8"/>
-      <c r="N88" s="8"/>
-      <c r="O88" s="8"/>
-      <c r="P88" s="8"/>
-      <c r="Q88" s="8"/>
-      <c r="R88" s="8"/>
-      <c r="S88" s="8"/>
-      <c r="T88" s="8"/>
-      <c r="U88" s="8"/>
-      <c r="V88" s="8"/>
-      <c r="W88" s="8"/>
-      <c r="X88" s="8"/>
-      <c r="Y88" s="8"/>
-      <c r="Z88" s="8"/>
+      <c r="B88" s="14">
+        <v>67017.0</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F88" s="12">
+        <v>100000.0</v>
+      </c>
+      <c r="G88" s="10"/>
+      <c r="H88" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I88" s="9"/>
+      <c r="J88" s="9"/>
+      <c r="K88" s="9"/>
+      <c r="L88" s="9"/>
+      <c r="M88" s="9"/>
+      <c r="N88" s="9"/>
+      <c r="O88" s="9"/>
+      <c r="P88" s="9"/>
+      <c r="Q88" s="9"/>
+      <c r="R88" s="9"/>
+      <c r="S88" s="9"/>
+      <c r="T88" s="9"/>
+      <c r="U88" s="9"/>
+      <c r="V88" s="9"/>
+      <c r="W88" s="9"/>
+      <c r="X88" s="9"/>
+      <c r="Y88" s="9"/>
+      <c r="Z88" s="9"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="3">
         <v>197.0</v>
       </c>
-      <c r="B89" s="7"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="7"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="7"/>
-      <c r="G89" s="7"/>
-      <c r="H89" s="7"/>
-      <c r="I89" s="8"/>
-      <c r="J89" s="8"/>
-      <c r="K89" s="8"/>
-      <c r="L89" s="8"/>
-      <c r="M89" s="8"/>
-      <c r="N89" s="8"/>
-      <c r="O89" s="8"/>
-      <c r="P89" s="8"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
-      <c r="S89" s="8"/>
-      <c r="T89" s="8"/>
-      <c r="U89" s="8"/>
-      <c r="V89" s="8"/>
-      <c r="W89" s="8"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="8"/>
-      <c r="Z89" s="8"/>
+      <c r="B89" s="14">
+        <v>67017.0</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F89" s="8">
+        <v>30000.0</v>
+      </c>
+      <c r="G89" s="13"/>
+      <c r="H89" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I89" s="9"/>
+      <c r="J89" s="9"/>
+      <c r="K89" s="9"/>
+      <c r="L89" s="9"/>
+      <c r="M89" s="9"/>
+      <c r="N89" s="9"/>
+      <c r="O89" s="9"/>
+      <c r="P89" s="9"/>
+      <c r="Q89" s="9"/>
+      <c r="R89" s="9"/>
+      <c r="S89" s="9"/>
+      <c r="T89" s="9"/>
+      <c r="U89" s="9"/>
+      <c r="V89" s="9"/>
+      <c r="W89" s="9"/>
+      <c r="X89" s="9"/>
+      <c r="Y89" s="9"/>
+      <c r="Z89" s="9"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="3">
         <v>198.0</v>
       </c>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9"/>
-      <c r="F90" s="9"/>
-      <c r="G90" s="9"/>
-      <c r="H90" s="9"/>
-      <c r="I90" s="8"/>
-      <c r="J90" s="8"/>
-      <c r="K90" s="8"/>
-      <c r="L90" s="8"/>
-      <c r="M90" s="8"/>
-      <c r="N90" s="8"/>
-      <c r="O90" s="8"/>
-      <c r="P90" s="8"/>
-      <c r="Q90" s="8"/>
-      <c r="R90" s="8"/>
-      <c r="S90" s="8"/>
-      <c r="T90" s="8"/>
-      <c r="U90" s="8"/>
-      <c r="V90" s="8"/>
-      <c r="W90" s="8"/>
-      <c r="X90" s="8"/>
-      <c r="Y90" s="8"/>
-      <c r="Z90" s="8"/>
+      <c r="B90" s="14">
+        <v>67019.0</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F90" s="12">
+        <v>20000.0</v>
+      </c>
+      <c r="G90" s="10"/>
+      <c r="H90" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I90" s="9"/>
+      <c r="J90" s="9"/>
+      <c r="K90" s="9"/>
+      <c r="L90" s="9"/>
+      <c r="M90" s="9"/>
+      <c r="N90" s="9"/>
+      <c r="O90" s="9"/>
+      <c r="P90" s="9"/>
+      <c r="Q90" s="9"/>
+      <c r="R90" s="9"/>
+      <c r="S90" s="9"/>
+      <c r="T90" s="9"/>
+      <c r="U90" s="9"/>
+      <c r="V90" s="9"/>
+      <c r="W90" s="9"/>
+      <c r="X90" s="9"/>
+      <c r="Y90" s="9"/>
+      <c r="Z90" s="9"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="3">
         <v>199.0</v>
       </c>
-      <c r="B91" s="7"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="7"/>
-      <c r="E91" s="7"/>
-      <c r="F91" s="7"/>
-      <c r="G91" s="7"/>
-      <c r="H91" s="7"/>
-      <c r="I91" s="8"/>
-      <c r="J91" s="8"/>
-      <c r="K91" s="8"/>
-      <c r="L91" s="8"/>
-      <c r="M91" s="8"/>
-      <c r="N91" s="8"/>
-      <c r="O91" s="8"/>
-      <c r="P91" s="8"/>
-      <c r="Q91" s="8"/>
-      <c r="R91" s="8"/>
-      <c r="S91" s="8"/>
-      <c r="T91" s="8"/>
-      <c r="U91" s="8"/>
-      <c r="V91" s="8"/>
-      <c r="W91" s="8"/>
-      <c r="X91" s="8"/>
-      <c r="Y91" s="8"/>
-      <c r="Z91" s="8"/>
+      <c r="B91" s="14">
+        <v>67019.0</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F91" s="8">
+        <v>50000.0</v>
+      </c>
+      <c r="G91" s="13"/>
+      <c r="H91" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I91" s="9"/>
+      <c r="J91" s="9"/>
+      <c r="K91" s="9"/>
+      <c r="L91" s="9"/>
+      <c r="M91" s="9"/>
+      <c r="N91" s="9"/>
+      <c r="O91" s="9"/>
+      <c r="P91" s="9"/>
+      <c r="Q91" s="9"/>
+      <c r="R91" s="9"/>
+      <c r="S91" s="9"/>
+      <c r="T91" s="9"/>
+      <c r="U91" s="9"/>
+      <c r="V91" s="9"/>
+      <c r="W91" s="9"/>
+      <c r="X91" s="9"/>
+      <c r="Y91" s="9"/>
+      <c r="Z91" s="9"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="3">
         <v>200.0</v>
       </c>
-      <c r="B92" s="9"/>
-      <c r="C92" s="9"/>
-      <c r="D92" s="9"/>
-      <c r="E92" s="9"/>
-      <c r="F92" s="9"/>
-      <c r="G92" s="9"/>
-      <c r="H92" s="9"/>
-      <c r="I92" s="8"/>
-      <c r="J92" s="8"/>
-      <c r="K92" s="8"/>
-      <c r="L92" s="8"/>
-      <c r="M92" s="8"/>
-      <c r="N92" s="8"/>
-      <c r="O92" s="8"/>
-      <c r="P92" s="8"/>
-      <c r="Q92" s="8"/>
-      <c r="R92" s="8"/>
-      <c r="S92" s="8"/>
-      <c r="T92" s="8"/>
-      <c r="U92" s="8"/>
-      <c r="V92" s="8"/>
-      <c r="W92" s="8"/>
-      <c r="X92" s="8"/>
-      <c r="Y92" s="8"/>
-      <c r="Z92" s="8"/>
+      <c r="B92" s="14">
+        <v>67020.0</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F92" s="12">
+        <v>100000.0</v>
+      </c>
+      <c r="G92" s="10"/>
+      <c r="H92" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I92" s="9"/>
+      <c r="J92" s="9"/>
+      <c r="K92" s="9"/>
+      <c r="L92" s="9"/>
+      <c r="M92" s="9"/>
+      <c r="N92" s="9"/>
+      <c r="O92" s="9"/>
+      <c r="P92" s="9"/>
+      <c r="Q92" s="9"/>
+      <c r="R92" s="9"/>
+      <c r="S92" s="9"/>
+      <c r="T92" s="9"/>
+      <c r="U92" s="9"/>
+      <c r="V92" s="9"/>
+      <c r="W92" s="9"/>
+      <c r="X92" s="9"/>
+      <c r="Y92" s="9"/>
+      <c r="Z92" s="9"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="3">
         <v>201.0</v>
       </c>
-      <c r="B93" s="7"/>
-      <c r="C93" s="7"/>
-      <c r="D93" s="7"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="7"/>
-      <c r="G93" s="7"/>
-      <c r="H93" s="7"/>
-      <c r="I93" s="8"/>
-      <c r="J93" s="8"/>
-      <c r="K93" s="8"/>
-      <c r="L93" s="8"/>
-      <c r="M93" s="8"/>
-      <c r="N93" s="8"/>
-      <c r="O93" s="8"/>
-      <c r="P93" s="8"/>
-      <c r="Q93" s="8"/>
-      <c r="R93" s="8"/>
-      <c r="S93" s="8"/>
-      <c r="T93" s="8"/>
-      <c r="U93" s="8"/>
-      <c r="V93" s="8"/>
-      <c r="W93" s="8"/>
-      <c r="X93" s="8"/>
-      <c r="Y93" s="8"/>
-      <c r="Z93" s="8"/>
+      <c r="B93" s="13"/>
+      <c r="C93" s="13"/>
+      <c r="D93" s="13"/>
+      <c r="E93" s="13"/>
+      <c r="F93" s="13"/>
+      <c r="G93" s="13"/>
+      <c r="H93" s="13"/>
+      <c r="I93" s="9"/>
+      <c r="J93" s="9"/>
+      <c r="K93" s="9"/>
+      <c r="L93" s="9"/>
+      <c r="M93" s="9"/>
+      <c r="N93" s="9"/>
+      <c r="O93" s="9"/>
+      <c r="P93" s="9"/>
+      <c r="Q93" s="9"/>
+      <c r="R93" s="9"/>
+      <c r="S93" s="9"/>
+      <c r="T93" s="9"/>
+      <c r="U93" s="9"/>
+      <c r="V93" s="9"/>
+      <c r="W93" s="9"/>
+      <c r="X93" s="9"/>
+      <c r="Y93" s="9"/>
+      <c r="Z93" s="9"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="3">
         <v>202.0</v>
       </c>
-      <c r="B94" s="9"/>
-      <c r="C94" s="9"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="9"/>
-      <c r="F94" s="9"/>
-      <c r="G94" s="9"/>
-      <c r="H94" s="9"/>
-      <c r="I94" s="8"/>
-      <c r="J94" s="8"/>
-      <c r="K94" s="8"/>
-      <c r="L94" s="8"/>
-      <c r="M94" s="8"/>
-      <c r="N94" s="8"/>
-      <c r="O94" s="8"/>
-      <c r="P94" s="8"/>
-      <c r="Q94" s="8"/>
-      <c r="R94" s="8"/>
-      <c r="S94" s="8"/>
-      <c r="T94" s="8"/>
-      <c r="U94" s="8"/>
-      <c r="V94" s="8"/>
-      <c r="W94" s="8"/>
-      <c r="X94" s="8"/>
-      <c r="Y94" s="8"/>
-      <c r="Z94" s="8"/>
+      <c r="B94" s="10"/>
+      <c r="C94" s="10"/>
+      <c r="D94" s="10"/>
+      <c r="E94" s="10"/>
+      <c r="F94" s="10"/>
+      <c r="G94" s="10"/>
+      <c r="H94" s="10"/>
+      <c r="I94" s="9"/>
+      <c r="J94" s="9"/>
+      <c r="K94" s="9"/>
+      <c r="L94" s="9"/>
+      <c r="M94" s="9"/>
+      <c r="N94" s="9"/>
+      <c r="O94" s="9"/>
+      <c r="P94" s="9"/>
+      <c r="Q94" s="9"/>
+      <c r="R94" s="9"/>
+      <c r="S94" s="9"/>
+      <c r="T94" s="9"/>
+      <c r="U94" s="9"/>
+      <c r="V94" s="9"/>
+      <c r="W94" s="9"/>
+      <c r="X94" s="9"/>
+      <c r="Y94" s="9"/>
+      <c r="Z94" s="9"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="3">
         <v>203.0</v>
       </c>
-      <c r="B95" s="7"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7"/>
-      <c r="G95" s="7"/>
-      <c r="H95" s="7"/>
-      <c r="I95" s="8"/>
-      <c r="J95" s="8"/>
-      <c r="K95" s="8"/>
-      <c r="L95" s="8"/>
-      <c r="M95" s="8"/>
-      <c r="N95" s="8"/>
-      <c r="O95" s="8"/>
-      <c r="P95" s="8"/>
-      <c r="Q95" s="8"/>
-      <c r="R95" s="8"/>
-      <c r="S95" s="8"/>
-      <c r="T95" s="8"/>
-      <c r="U95" s="8"/>
-      <c r="V95" s="8"/>
-      <c r="W95" s="8"/>
-      <c r="X95" s="8"/>
-      <c r="Y95" s="8"/>
-      <c r="Z95" s="8"/>
+      <c r="B95" s="13"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="13"/>
+      <c r="E95" s="13"/>
+      <c r="F95" s="13"/>
+      <c r="G95" s="13"/>
+      <c r="H95" s="13"/>
+      <c r="I95" s="9"/>
+      <c r="J95" s="9"/>
+      <c r="K95" s="9"/>
+      <c r="L95" s="9"/>
+      <c r="M95" s="9"/>
+      <c r="N95" s="9"/>
+      <c r="O95" s="9"/>
+      <c r="P95" s="9"/>
+      <c r="Q95" s="9"/>
+      <c r="R95" s="9"/>
+      <c r="S95" s="9"/>
+      <c r="T95" s="9"/>
+      <c r="U95" s="9"/>
+      <c r="V95" s="9"/>
+      <c r="W95" s="9"/>
+      <c r="X95" s="9"/>
+      <c r="Y95" s="9"/>
+      <c r="Z95" s="9"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="3">
         <v>204.0</v>
       </c>
-      <c r="B96" s="9"/>
-      <c r="C96" s="9"/>
-      <c r="D96" s="9"/>
-      <c r="E96" s="9"/>
-      <c r="F96" s="9"/>
-      <c r="G96" s="9"/>
-      <c r="H96" s="9"/>
-      <c r="I96" s="8"/>
-      <c r="J96" s="8"/>
-      <c r="K96" s="8"/>
-      <c r="L96" s="8"/>
-      <c r="M96" s="8"/>
-      <c r="N96" s="8"/>
-      <c r="O96" s="8"/>
-      <c r="P96" s="8"/>
-      <c r="Q96" s="8"/>
-      <c r="R96" s="8"/>
-      <c r="S96" s="8"/>
-      <c r="T96" s="8"/>
-      <c r="U96" s="8"/>
-      <c r="V96" s="8"/>
-      <c r="W96" s="8"/>
-      <c r="X96" s="8"/>
-      <c r="Y96" s="8"/>
-      <c r="Z96" s="8"/>
+      <c r="B96" s="10"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="10"/>
+      <c r="E96" s="10"/>
+      <c r="F96" s="10"/>
+      <c r="G96" s="10"/>
+      <c r="H96" s="10"/>
+      <c r="I96" s="9"/>
+      <c r="J96" s="9"/>
+      <c r="K96" s="9"/>
+      <c r="L96" s="9"/>
+      <c r="M96" s="9"/>
+      <c r="N96" s="9"/>
+      <c r="O96" s="9"/>
+      <c r="P96" s="9"/>
+      <c r="Q96" s="9"/>
+      <c r="R96" s="9"/>
+      <c r="S96" s="9"/>
+      <c r="T96" s="9"/>
+      <c r="U96" s="9"/>
+      <c r="V96" s="9"/>
+      <c r="W96" s="9"/>
+      <c r="X96" s="9"/>
+      <c r="Y96" s="9"/>
+      <c r="Z96" s="9"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="3">
         <v>205.0</v>
       </c>
-      <c r="B97" s="7"/>
-      <c r="C97" s="7"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="7"/>
-      <c r="F97" s="7"/>
-      <c r="G97" s="7"/>
-      <c r="H97" s="7"/>
-      <c r="I97" s="8"/>
-      <c r="J97" s="8"/>
-      <c r="K97" s="8"/>
-      <c r="L97" s="8"/>
-      <c r="M97" s="8"/>
-      <c r="N97" s="8"/>
-      <c r="O97" s="8"/>
-      <c r="P97" s="8"/>
-      <c r="Q97" s="8"/>
-      <c r="R97" s="8"/>
-      <c r="S97" s="8"/>
-      <c r="T97" s="8"/>
-      <c r="U97" s="8"/>
-      <c r="V97" s="8"/>
-      <c r="W97" s="8"/>
-      <c r="X97" s="8"/>
-      <c r="Y97" s="8"/>
-      <c r="Z97" s="8"/>
+      <c r="B97" s="13"/>
+      <c r="C97" s="13"/>
+      <c r="D97" s="13"/>
+      <c r="E97" s="13"/>
+      <c r="F97" s="13"/>
+      <c r="G97" s="13"/>
+      <c r="H97" s="13"/>
+      <c r="I97" s="9"/>
+      <c r="J97" s="9"/>
+      <c r="K97" s="9"/>
+      <c r="L97" s="9"/>
+      <c r="M97" s="9"/>
+      <c r="N97" s="9"/>
+      <c r="O97" s="9"/>
+      <c r="P97" s="9"/>
+      <c r="Q97" s="9"/>
+      <c r="R97" s="9"/>
+      <c r="S97" s="9"/>
+      <c r="T97" s="9"/>
+      <c r="U97" s="9"/>
+      <c r="V97" s="9"/>
+      <c r="W97" s="9"/>
+      <c r="X97" s="9"/>
+      <c r="Y97" s="9"/>
+      <c r="Z97" s="9"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="3">
         <v>206.0</v>
       </c>
-      <c r="B98" s="9"/>
-      <c r="C98" s="9"/>
-      <c r="D98" s="9"/>
-      <c r="E98" s="9"/>
-      <c r="F98" s="9"/>
-      <c r="G98" s="9"/>
-      <c r="H98" s="9"/>
-      <c r="I98" s="8"/>
-      <c r="J98" s="8"/>
-      <c r="K98" s="8"/>
-      <c r="L98" s="8"/>
-      <c r="M98" s="8"/>
-      <c r="N98" s="8"/>
-      <c r="O98" s="8"/>
-      <c r="P98" s="8"/>
-      <c r="Q98" s="8"/>
-      <c r="R98" s="8"/>
-      <c r="S98" s="8"/>
-      <c r="T98" s="8"/>
-      <c r="U98" s="8"/>
-      <c r="V98" s="8"/>
-      <c r="W98" s="8"/>
-      <c r="X98" s="8"/>
-      <c r="Y98" s="8"/>
-      <c r="Z98" s="8"/>
+      <c r="B98" s="10"/>
+      <c r="C98" s="10"/>
+      <c r="D98" s="10"/>
+      <c r="E98" s="10"/>
+      <c r="F98" s="10"/>
+      <c r="G98" s="10"/>
+      <c r="H98" s="10"/>
+      <c r="I98" s="9"/>
+      <c r="J98" s="9"/>
+      <c r="K98" s="9"/>
+      <c r="L98" s="9"/>
+      <c r="M98" s="9"/>
+      <c r="N98" s="9"/>
+      <c r="O98" s="9"/>
+      <c r="P98" s="9"/>
+      <c r="Q98" s="9"/>
+      <c r="R98" s="9"/>
+      <c r="S98" s="9"/>
+      <c r="T98" s="9"/>
+      <c r="U98" s="9"/>
+      <c r="V98" s="9"/>
+      <c r="W98" s="9"/>
+      <c r="X98" s="9"/>
+      <c r="Y98" s="9"/>
+      <c r="Z98" s="9"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="3">
         <v>207.0</v>
       </c>
-      <c r="B99" s="7"/>
-      <c r="C99" s="7"/>
-      <c r="D99" s="7"/>
-      <c r="E99" s="7"/>
-      <c r="F99" s="7"/>
-      <c r="G99" s="7"/>
-      <c r="H99" s="7"/>
-      <c r="I99" s="8"/>
-      <c r="J99" s="8"/>
-      <c r="K99" s="8"/>
-      <c r="L99" s="8"/>
-      <c r="M99" s="8"/>
-      <c r="N99" s="8"/>
-      <c r="O99" s="8"/>
-      <c r="P99" s="8"/>
-      <c r="Q99" s="8"/>
-      <c r="R99" s="8"/>
-      <c r="S99" s="8"/>
-      <c r="T99" s="8"/>
-      <c r="U99" s="8"/>
-      <c r="V99" s="8"/>
-      <c r="W99" s="8"/>
-      <c r="X99" s="8"/>
-      <c r="Y99" s="8"/>
-      <c r="Z99" s="8"/>
+      <c r="B99" s="13"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="13"/>
+      <c r="E99" s="13"/>
+      <c r="F99" s="13"/>
+      <c r="G99" s="13"/>
+      <c r="H99" s="13"/>
+      <c r="I99" s="9"/>
+      <c r="J99" s="9"/>
+      <c r="K99" s="9"/>
+      <c r="L99" s="9"/>
+      <c r="M99" s="9"/>
+      <c r="N99" s="9"/>
+      <c r="O99" s="9"/>
+      <c r="P99" s="9"/>
+      <c r="Q99" s="9"/>
+      <c r="R99" s="9"/>
+      <c r="S99" s="9"/>
+      <c r="T99" s="9"/>
+      <c r="U99" s="9"/>
+      <c r="V99" s="9"/>
+      <c r="W99" s="9"/>
+      <c r="X99" s="9"/>
+      <c r="Y99" s="9"/>
+      <c r="Z99" s="9"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="3">
         <v>208.0</v>
       </c>
-      <c r="B100" s="9"/>
-      <c r="C100" s="9"/>
-      <c r="D100" s="9"/>
-      <c r="E100" s="9"/>
-      <c r="F100" s="9"/>
-      <c r="G100" s="9"/>
-      <c r="H100" s="9"/>
-      <c r="I100" s="8"/>
-      <c r="J100" s="8"/>
-      <c r="K100" s="8"/>
-      <c r="L100" s="8"/>
-      <c r="M100" s="8"/>
-      <c r="N100" s="8"/>
-      <c r="O100" s="8"/>
-      <c r="P100" s="8"/>
-      <c r="Q100" s="8"/>
-      <c r="R100" s="8"/>
-      <c r="S100" s="8"/>
-      <c r="T100" s="8"/>
-      <c r="U100" s="8"/>
-      <c r="V100" s="8"/>
-      <c r="W100" s="8"/>
-      <c r="X100" s="8"/>
-      <c r="Y100" s="8"/>
-      <c r="Z100" s="8"/>
+      <c r="B100" s="10"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="10"/>
+      <c r="E100" s="10"/>
+      <c r="F100" s="10"/>
+      <c r="G100" s="10"/>
+      <c r="H100" s="10"/>
+      <c r="I100" s="9"/>
+      <c r="J100" s="9"/>
+      <c r="K100" s="9"/>
+      <c r="L100" s="9"/>
+      <c r="M100" s="9"/>
+      <c r="N100" s="9"/>
+      <c r="O100" s="9"/>
+      <c r="P100" s="9"/>
+      <c r="Q100" s="9"/>
+      <c r="R100" s="9"/>
+      <c r="S100" s="9"/>
+      <c r="T100" s="9"/>
+      <c r="U100" s="9"/>
+      <c r="V100" s="9"/>
+      <c r="W100" s="9"/>
+      <c r="X100" s="9"/>
+      <c r="Y100" s="9"/>
+      <c r="Z100" s="9"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="3">
         <v>209.0</v>
       </c>
-      <c r="B101" s="7"/>
-      <c r="C101" s="7"/>
-      <c r="D101" s="7"/>
-      <c r="E101" s="7"/>
-      <c r="F101" s="7"/>
-      <c r="G101" s="7"/>
-      <c r="H101" s="7"/>
-      <c r="I101" s="8"/>
-      <c r="J101" s="8"/>
-      <c r="K101" s="8"/>
-      <c r="L101" s="8"/>
-      <c r="M101" s="8"/>
-      <c r="N101" s="8"/>
-      <c r="O101" s="8"/>
-      <c r="P101" s="8"/>
-      <c r="Q101" s="8"/>
-      <c r="R101" s="8"/>
-      <c r="S101" s="8"/>
-      <c r="T101" s="8"/>
-      <c r="U101" s="8"/>
-      <c r="V101" s="8"/>
-      <c r="W101" s="8"/>
-      <c r="X101" s="8"/>
-      <c r="Y101" s="8"/>
-      <c r="Z101" s="8"/>
+      <c r="B101" s="13"/>
+      <c r="C101" s="13"/>
+      <c r="D101" s="13"/>
+      <c r="E101" s="13"/>
+      <c r="F101" s="13"/>
+      <c r="G101" s="13"/>
+      <c r="H101" s="13"/>
+      <c r="I101" s="9"/>
+      <c r="J101" s="9"/>
+      <c r="K101" s="9"/>
+      <c r="L101" s="9"/>
+      <c r="M101" s="9"/>
+      <c r="N101" s="9"/>
+      <c r="O101" s="9"/>
+      <c r="P101" s="9"/>
+      <c r="Q101" s="9"/>
+      <c r="R101" s="9"/>
+      <c r="S101" s="9"/>
+      <c r="T101" s="9"/>
+      <c r="U101" s="9"/>
+      <c r="V101" s="9"/>
+      <c r="W101" s="9"/>
+      <c r="X101" s="9"/>
+      <c r="Y101" s="9"/>
+      <c r="Z101" s="9"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="3">
         <v>210.0</v>
       </c>
-      <c r="B102" s="9"/>
-      <c r="C102" s="9"/>
-      <c r="D102" s="9"/>
-      <c r="E102" s="9"/>
-      <c r="F102" s="9"/>
-      <c r="G102" s="9"/>
-      <c r="H102" s="9"/>
-      <c r="I102" s="8"/>
-      <c r="J102" s="8"/>
-      <c r="K102" s="8"/>
-      <c r="L102" s="8"/>
-      <c r="M102" s="8"/>
-      <c r="N102" s="8"/>
-      <c r="O102" s="8"/>
-      <c r="P102" s="8"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="8"/>
-      <c r="U102" s="8"/>
-      <c r="V102" s="8"/>
-      <c r="W102" s="8"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="8"/>
-      <c r="Z102" s="8"/>
+      <c r="B102" s="10"/>
+      <c r="C102" s="10"/>
+      <c r="D102" s="10"/>
+      <c r="E102" s="10"/>
+      <c r="F102" s="10"/>
+      <c r="G102" s="10"/>
+      <c r="H102" s="10"/>
+      <c r="I102" s="9"/>
+      <c r="J102" s="9"/>
+      <c r="K102" s="9"/>
+      <c r="L102" s="9"/>
+      <c r="M102" s="9"/>
+      <c r="N102" s="9"/>
+      <c r="O102" s="9"/>
+      <c r="P102" s="9"/>
+      <c r="Q102" s="9"/>
+      <c r="R102" s="9"/>
+      <c r="S102" s="9"/>
+      <c r="T102" s="9"/>
+      <c r="U102" s="9"/>
+      <c r="V102" s="9"/>
+      <c r="W102" s="9"/>
+      <c r="X102" s="9"/>
+      <c r="Y102" s="9"/>
+      <c r="Z102" s="9"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="3">
         <v>211.0</v>
       </c>
-      <c r="B103" s="7"/>
-      <c r="C103" s="7"/>
-      <c r="D103" s="7"/>
-      <c r="E103" s="7"/>
-      <c r="F103" s="7"/>
-      <c r="G103" s="7"/>
-      <c r="H103" s="7"/>
-      <c r="I103" s="8"/>
-      <c r="J103" s="8"/>
-      <c r="K103" s="8"/>
-      <c r="L103" s="8"/>
-      <c r="M103" s="8"/>
-      <c r="N103" s="8"/>
-      <c r="O103" s="8"/>
-      <c r="P103" s="8"/>
-      <c r="Q103" s="8"/>
-      <c r="R103" s="8"/>
-      <c r="S103" s="8"/>
-      <c r="T103" s="8"/>
-      <c r="U103" s="8"/>
-      <c r="V103" s="8"/>
-      <c r="W103" s="8"/>
-      <c r="X103" s="8"/>
-      <c r="Y103" s="8"/>
-      <c r="Z103" s="8"/>
+      <c r="B103" s="13"/>
+      <c r="C103" s="13"/>
+      <c r="D103" s="13"/>
+      <c r="E103" s="13"/>
+      <c r="F103" s="13"/>
+      <c r="G103" s="13"/>
+      <c r="H103" s="13"/>
+      <c r="I103" s="9"/>
+      <c r="J103" s="9"/>
+      <c r="K103" s="9"/>
+      <c r="L103" s="9"/>
+      <c r="M103" s="9"/>
+      <c r="N103" s="9"/>
+      <c r="O103" s="9"/>
+      <c r="P103" s="9"/>
+      <c r="Q103" s="9"/>
+      <c r="R103" s="9"/>
+      <c r="S103" s="9"/>
+      <c r="T103" s="9"/>
+      <c r="U103" s="9"/>
+      <c r="V103" s="9"/>
+      <c r="W103" s="9"/>
+      <c r="X103" s="9"/>
+      <c r="Y103" s="9"/>
+      <c r="Z103" s="9"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="3">
         <v>212.0</v>
       </c>
-      <c r="B104" s="9"/>
-      <c r="C104" s="9"/>
-      <c r="D104" s="9"/>
-      <c r="E104" s="9"/>
-      <c r="F104" s="9"/>
-      <c r="G104" s="9"/>
-      <c r="H104" s="9"/>
-      <c r="I104" s="8"/>
-      <c r="J104" s="8"/>
-      <c r="K104" s="8"/>
-      <c r="L104" s="8"/>
-      <c r="M104" s="8"/>
-      <c r="N104" s="8"/>
-      <c r="O104" s="8"/>
-      <c r="P104" s="8"/>
-      <c r="Q104" s="8"/>
-      <c r="R104" s="8"/>
-      <c r="S104" s="8"/>
-      <c r="T104" s="8"/>
-      <c r="U104" s="8"/>
-      <c r="V104" s="8"/>
-      <c r="W104" s="8"/>
-      <c r="X104" s="8"/>
-      <c r="Y104" s="8"/>
-      <c r="Z104" s="8"/>
+      <c r="B104" s="10"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="10"/>
+      <c r="E104" s="10"/>
+      <c r="F104" s="10"/>
+      <c r="G104" s="10"/>
+      <c r="H104" s="10"/>
+      <c r="I104" s="9"/>
+      <c r="J104" s="9"/>
+      <c r="K104" s="9"/>
+      <c r="L104" s="9"/>
+      <c r="M104" s="9"/>
+      <c r="N104" s="9"/>
+      <c r="O104" s="9"/>
+      <c r="P104" s="9"/>
+      <c r="Q104" s="9"/>
+      <c r="R104" s="9"/>
+      <c r="S104" s="9"/>
+      <c r="T104" s="9"/>
+      <c r="U104" s="9"/>
+      <c r="V104" s="9"/>
+      <c r="W104" s="9"/>
+      <c r="X104" s="9"/>
+      <c r="Y104" s="9"/>
+      <c r="Z104" s="9"/>
     </row>
     <row r="105" ht="15.75" customHeight="1"/>
     <row r="106" ht="15.75" customHeight="1"/>
